--- a/products/friction_pendulum_embedded_parts/excel_template.xlsx
+++ b/products/friction_pendulum_embedded_parts/excel_template.xlsx
@@ -541,13 +541,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -571,6 +578,41 @@
           <t>生产日期</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>预埋板边长(mm)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>预埋板厚度(mm)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>螺栓孔位置(mm)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>组件直径(mm)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>组件长度(mm)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>组件数量倍数</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>钢板牌号</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -591,6 +633,13 @@
           <t>2026年5月</t>
         </is>
       </c>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -611,6 +660,13 @@
           <t>2026年5月</t>
         </is>
       </c>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -623,7 +679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -667,7 +723,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5. 钢板材质单按厚度和Q235B自动匹配最新有效证书。</t>
+          <t>5. 表格中的边长、厚度、孔位、组件尺寸和数量倍数都可以手动填写；留空则按标准参数自动带出。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>6. 钢板材质单按厚度和Q235B自动匹配最新有效证书；如钢板牌号填写其它值，则按填写值匹配。</t>
         </is>
       </c>
     </row>
